--- a/docs/downloads/04/tbl_other_write_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_write_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
